--- a/data/trans_bre/P2A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 6,1</t>
+          <t>-15,93; 6,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 22,72</t>
+          <t>-4,41; 21,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 16,41</t>
+          <t>-9,13; 16,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 16,37</t>
+          <t>-6,92; 18,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,58; 27,44</t>
+          <t>-47,0; 28,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 126,79</t>
+          <t>-15,7; 115,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 61,05</t>
+          <t>-25,2; 61,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 25,49</t>
+          <t>-8,96; 27,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 9,42</t>
+          <t>-20,46; 6,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 19,46</t>
+          <t>-7,77; 18,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 10,34</t>
+          <t>-11,68; 10,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 3,35</t>
+          <t>-16,0; 3,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 26,75</t>
+          <t>-39,42; 18,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 79,27</t>
+          <t>-21,0; 74,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 41,73</t>
+          <t>-32,34; 41,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,94; 4,2</t>
+          <t>-18,46; 3,93</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 9,17</t>
+          <t>-15,32; 8,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 20,34</t>
+          <t>-6,35; 20,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 10,26</t>
+          <t>-19,5; 9,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 20,04</t>
+          <t>-6,2; 19,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 40,73</t>
+          <t>-45,76; 36,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 86,39</t>
+          <t>-16,44; 87,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,42; 41,57</t>
+          <t>-50,5; 35,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 29,06</t>
+          <t>-7,03; 28,11</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 5,47</t>
+          <t>-13,75; 4,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 6,95</t>
+          <t>-12,21; 6,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 12,84</t>
+          <t>-3,89; 13,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 12,05</t>
+          <t>-7,17; 12,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 17,29</t>
+          <t>-32,14; 13,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 20,46</t>
+          <t>-26,91; 17,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 49,55</t>
+          <t>-10,64; 49,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 16,82</t>
+          <t>-9,03; 18,35</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 2,76</t>
+          <t>-22,57; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 2,29</t>
+          <t>-20,93; 1,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 4,09</t>
+          <t>-18,88; 3,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 28,06</t>
+          <t>1,93; 26,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,7; 6,98</t>
+          <t>-45,68; 7,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,13; 7,9</t>
+          <t>-46,73; 3,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,83; 10,89</t>
+          <t>-37,7; 9,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 53,34</t>
+          <t>2,56; 48,22</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 15,77</t>
+          <t>-10,85; 14,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 15,69</t>
+          <t>-12,82; 15,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 20,7</t>
+          <t>-6,62; 21,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,41; -0,86</t>
+          <t>-24,32; 0,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 48,53</t>
+          <t>-23,73; 46,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 52,71</t>
+          <t>-30,27; 51,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 97,1</t>
+          <t>-19,53; 106,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,33; -1,08</t>
+          <t>-27,46; 0,31</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 0,28</t>
+          <t>-9,38; 0,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,23</t>
+          <t>-4,91; 4,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,69</t>
+          <t>-3,66; 5,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 8,16</t>
+          <t>-2,35; 8,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 0,87</t>
+          <t>-23,67; 0,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 16,12</t>
+          <t>-12,58; 15,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 18,38</t>
+          <t>-10,36; 18,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,42</t>
+          <t>-2,97; 11,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 6,19</t>
+          <t>-16,89; 6,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 21,81</t>
+          <t>-3,88; 22,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 16,15</t>
+          <t>-9,31; 16,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 18,2</t>
+          <t>-6,67; 16,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 28,31</t>
+          <t>-46,67; 28,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 115,07</t>
+          <t>-13,81; 118,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 61,36</t>
+          <t>-24,54; 60,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 27,89</t>
+          <t>-8,51; 25,98</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 6,78</t>
+          <t>-19,18; 7,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 18,62</t>
+          <t>-7,85; 19,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 10,56</t>
+          <t>-12,27; 10,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 3,11</t>
+          <t>-16,84; 3,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,42; 18,72</t>
+          <t>-39,77; 22,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 74,37</t>
+          <t>-20,4; 81,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 41,08</t>
+          <t>-33,43; 39,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 3,93</t>
+          <t>-19,31; 4,62</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 8,47</t>
+          <t>-13,83; 9,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 20,14</t>
+          <t>-5,67; 21,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 9,34</t>
+          <t>-19,18; 10,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 19,33</t>
+          <t>-5,23; 20,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 36,96</t>
+          <t>-42,13; 44,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 87,05</t>
+          <t>-14,89; 87,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 35,11</t>
+          <t>-47,95; 39,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 28,11</t>
+          <t>-6,23; 28,8</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 4,48</t>
+          <t>-12,94; 5,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 6,48</t>
+          <t>-12,33; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 13,19</t>
+          <t>-3,71; 12,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 12,78</t>
+          <t>-7,59; 12,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 13,5</t>
+          <t>-31,33; 15,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 17,69</t>
+          <t>-27,62; 18,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 49,3</t>
+          <t>-10,22; 46,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 18,35</t>
+          <t>-9,62; 16,88</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 2,86</t>
+          <t>-23,26; 1,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 1,36</t>
+          <t>-21,63; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 3,65</t>
+          <t>-17,5; 3,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 26,69</t>
+          <t>2,18; 27,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,68; 7,6</t>
+          <t>-45,51; 3,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 3,88</t>
+          <t>-47,13; 8,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 9,57</t>
+          <t>-36,61; 11,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 48,22</t>
+          <t>3,43; 52,89</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 14,96</t>
+          <t>-12,25; 14,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 15,88</t>
+          <t>-11,73; 15,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 21,93</t>
+          <t>-4,65; 21,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 0,27</t>
+          <t>-26,44; -1,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 46,76</t>
+          <t>-25,56; 42,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 51,97</t>
+          <t>-29,07; 48,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 106,81</t>
+          <t>-14,61; 99,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 0,31</t>
+          <t>-30,4; -2,34</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,29</t>
+          <t>-9,3; 0,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,98</t>
+          <t>-4,36; 5,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 5,71</t>
+          <t>-4,04; 5,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 8,2</t>
+          <t>-2,35; 8,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 0,93</t>
+          <t>-23,08; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 15,16</t>
+          <t>-11,71; 16,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 18,71</t>
+          <t>-11,38; 17,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 11,48</t>
+          <t>-3,06; 11,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 6,24</t>
+          <t>-17,0; 6,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 22,12</t>
+          <t>-3,59; 22,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 16,6</t>
+          <t>-10,41; 16,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 16,67</t>
+          <t>-10,15; 10,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-46,67; 28,97</t>
+          <t>-48,58; 27,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 118,33</t>
+          <t>-11,71; 126,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 60,11</t>
+          <t>-26,58; 61,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 25,98</t>
+          <t>-13,07; 14,92</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,32</t>
+          <t>-6,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,57%</t>
+          <t>-7,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 7,79</t>
+          <t>-17,89; 9,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 19,63</t>
+          <t>-7,71; 19,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 10,09</t>
+          <t>-11,61; 10,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 3,63</t>
+          <t>-17,01; 3,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,77; 22,43</t>
+          <t>-37,27; 26,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 81,91</t>
+          <t>-20,36; 79,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,43; 39,97</t>
+          <t>-33,86; 41,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 4,62</t>
+          <t>-19,27; 4,01</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>8,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 9,79</t>
+          <t>-15,6; 9,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 21,14</t>
+          <t>-5,64; 20,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 10,43</t>
+          <t>-18,29; 10,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 20,55</t>
+          <t>-3,13; 21,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 44,67</t>
+          <t>-46,03; 40,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 87,6</t>
+          <t>-14,85; 86,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,95; 39,81</t>
+          <t>-46,42; 41,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 28,8</t>
+          <t>-3,51; 32,13</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>-0,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 5,1</t>
+          <t>-12,85; 5,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 6,35</t>
+          <t>-12,12; 6,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 12,75</t>
+          <t>-3,51; 12,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 12,31</t>
+          <t>-7,42; 8,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 15,9</t>
+          <t>-30,97; 17,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 18,71</t>
+          <t>-26,77; 20,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 46,78</t>
+          <t>-10,14; 49,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 16,88</t>
+          <t>-9,31; 11,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>11,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>16,83%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 1,51</t>
+          <t>-21,75; 2,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 2,89</t>
+          <t>-20,65; 2,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 3,84</t>
+          <t>-19,85; 4,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 27,73</t>
+          <t>1,04; 24,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 3,87</t>
+          <t>-43,7; 6,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 8,28</t>
+          <t>-46,13; 7,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 11,29</t>
+          <t>-38,83; 10,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 52,89</t>
+          <t>2,27; 47,15</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-12,82</t>
+          <t>-14,02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-15,11%</t>
+          <t>-16,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 14,33</t>
+          <t>-10,64; 15,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 15,28</t>
+          <t>-12,19; 15,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 21,76</t>
+          <t>-5,7; 20,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-26,44; -1,63</t>
+          <t>-25,49; -2,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 42,11</t>
+          <t>-23,55; 48,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 48,95</t>
+          <t>-29,18; 52,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 99,32</t>
+          <t>-17,17; 97,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,4; -2,34</t>
+          <t>-28,82; -3,09</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 0,58</t>
+          <t>-9,19; 0,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 5,22</t>
+          <t>-5,12; 5,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 5,32</t>
+          <t>-3,69; 5,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 8,53</t>
+          <t>-3,26; 5,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 1,87</t>
+          <t>-23,04; 0,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 16,28</t>
+          <t>-13,43; 16,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 17,51</t>
+          <t>-10,33; 18,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 11,9</t>
+          <t>-4,19; 7,92</t>
         </is>
       </c>
     </row>
